--- a/data/pOXA48/rep1/counts.xlsx
+++ b/data/pOXA48/rep1/counts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/ceph/sysb/user/vuhien/AG Galardini/Hien/Scanner/20251106/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/storage/hien/Hien PhD project new/Result/Full lab evolution exp/pOXA48 plasmid/20251106 1st rep/Scanner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95CC324-9023-D447-82FB-2ABC2B3F4F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E9F85D-8A00-1C43-AA5D-C33D2056C172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19640" xr2:uid="{F0941CDE-55DC-E949-AB0F-9CFF344905A0}"/>
   </bookViews>
@@ -102,13 +102,13 @@
     <t>136h</t>
   </si>
   <si>
-    <t>150h</t>
+    <t>160h</t>
   </si>
   <si>
-    <t>174h</t>
+    <t>184h</t>
   </si>
   <si>
-    <t>198h</t>
+    <t>208h</t>
   </si>
 </sst>
 </file>
@@ -2558,7 +2558,7 @@
         <v>300</v>
       </c>
       <c r="E83">
-        <f t="shared" ref="E83:F83" si="0">3/0.01</f>
+        <f t="shared" ref="E83" si="0">3/0.01</f>
         <v>300</v>
       </c>
       <c r="F83">
